--- a/Demo.xlsx
+++ b/Demo.xlsx
@@ -8,26 +8,83 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUVRAJ\Desktop\My Activities\GitHub\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BE0792-85E2-493F-956E-0001022A1F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6209B6-C73C-4C98-AACA-7B17754959C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
   <si>
     <t>Sr. No</t>
+  </si>
+  <si>
+    <t>Name of Student</t>
+  </si>
+  <si>
+    <t>Sub1</t>
+  </si>
+  <si>
+    <t>Sub2</t>
+  </si>
+  <si>
+    <t>Sub3</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>%Age</t>
+  </si>
+  <si>
+    <t>Result</t>
   </si>
 </sst>
 </file>
@@ -63,8 +120,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -345,92 +404,399 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>90</v>
+      </c>
+      <c r="D2">
+        <v>79</v>
+      </c>
+      <c r="E2">
+        <v>44</v>
+      </c>
+      <c r="F2">
+        <f>SUM(C2:E2)</f>
+        <v>213</v>
+      </c>
+      <c r="G2">
+        <f>MAX(C2:E2)</f>
+        <v>90</v>
+      </c>
+      <c r="H2">
+        <f>MIN(C2:E2)</f>
+        <v>44</v>
+      </c>
+      <c r="I2" s="1">
+        <f>AVERAGE(C2:E2)</f>
+        <v>71</v>
+      </c>
+      <c r="J2" s="2">
+        <f>F2/300%</f>
+        <v>71</v>
+      </c>
+      <c r="K2" t="str">
+        <f>IF(J2&gt;=35,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>48</v>
+      </c>
+      <c r="D3">
+        <v>91</v>
+      </c>
+      <c r="E3">
+        <v>77</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F6" si="0">SUM(C3:E3)</f>
+        <v>216</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G6" si="1">MAX(C3:E3)</f>
+        <v>91</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H6" si="2">MIN(C3:E3)</f>
+        <v>48</v>
+      </c>
+      <c r="I3" s="1">
+        <f t="shared" ref="I3:I6" si="3">AVERAGE(C3:E3)</f>
+        <v>72</v>
+      </c>
+      <c r="J3" s="2">
+        <f t="shared" ref="J3:J6" si="4">F3/300%</f>
+        <v>72</v>
+      </c>
+      <c r="K3" t="str">
+        <f t="shared" ref="K3:K6" si="5">IF(J3&gt;=35,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>94</v>
+      </c>
+      <c r="D4">
+        <v>77</v>
+      </c>
+      <c r="E4">
+        <v>80</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>251</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="I4" s="1">
+        <f t="shared" si="3"/>
+        <v>83.666666666666671</v>
+      </c>
+      <c r="J4" s="2">
+        <f t="shared" si="4"/>
+        <v>83.666666666666671</v>
+      </c>
+      <c r="K4" t="str">
+        <f t="shared" si="5"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>90</v>
+      </c>
+      <c r="D5">
+        <v>44</v>
+      </c>
+      <c r="E5">
+        <v>55</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>189</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" si="3"/>
+        <v>63</v>
+      </c>
+      <c r="J5" s="2">
+        <f t="shared" si="4"/>
+        <v>63</v>
+      </c>
+      <c r="K5" t="str">
+        <f t="shared" si="5"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>62</v>
+      </c>
+      <c r="D6">
+        <v>78</v>
+      </c>
+      <c r="E6">
+        <v>77</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>217</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="2"/>
+        <v>62</v>
+      </c>
+      <c r="I6" s="1">
+        <f t="shared" si="3"/>
+        <v>72.333333333333329</v>
+      </c>
+      <c r="J6" s="2">
+        <f t="shared" si="4"/>
+        <v>72.333333333333329</v>
+      </c>
+      <c r="K6" t="str">
+        <f t="shared" si="5"/>
+        <v>Pass</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{269507E9-BEC7-4583-B3E5-5ECEC7CDD939}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="C2">
+        <v>90</v>
+      </c>
+      <c r="D2">
+        <v>79</v>
+      </c>
+      <c r="E2">
+        <v>44</v>
+      </c>
+      <c r="F2" t="str">
+        <f>IF(AND(C2&gt;=35,D2&gt;=35,E2&gt;=35),"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="C3">
+        <v>48</v>
+      </c>
+      <c r="D3">
+        <v>29</v>
+      </c>
+      <c r="E3">
+        <v>77</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F6" si="0">IF(AND(C3&gt;=35,D3&gt;=35,E3&gt;=35),"Pass","Fail")</f>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="C4">
+        <v>94</v>
+      </c>
+      <c r="D4">
+        <v>77</v>
+      </c>
+      <c r="E4">
+        <v>80</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="C5">
+        <v>90</v>
+      </c>
+      <c r="D5">
+        <v>44</v>
+      </c>
+      <c r="E5">
+        <v>55</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>16</v>
+      <c r="C6">
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>78</v>
+      </c>
+      <c r="E6">
+        <v>77</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
       </c>
     </row>
   </sheetData>

--- a/Demo.xlsx
+++ b/Demo.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUVRAJ\Desktop\My Activities\GitHub\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6209B6-C73C-4C98-AACA-7B17754959C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08ACABF2-5ED0-4012-AB1A-1DA1C99819A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>Sr. No</t>
   </si>
@@ -85,6 +86,42 @@
   </si>
   <si>
     <t>Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">df </t>
+  </si>
+  <si>
+    <t>Employee Name</t>
+  </si>
+  <si>
+    <t>Sr No</t>
+  </si>
+  <si>
+    <t>Performance rating</t>
+  </si>
+  <si>
+    <t>Promotion: Yes/No</t>
+  </si>
+  <si>
+    <t>Days(/180)</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>And condition</t>
+  </si>
+  <si>
+    <t>Or condition</t>
   </si>
 </sst>
 </file>
@@ -665,7 +702,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{269507E9-BEC7-4583-B3E5-5ECEC7CDD939}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
@@ -799,6 +836,254 @@
         <v>Fail</v>
       </c>
     </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF93C26-F917-4F20-A5B4-CE61275C5F48}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>117</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2" t="str">
+        <f>IF(AND(C2&gt;=130,D2&gt;=5),"Yes","No")</f>
+        <v>No</v>
+      </c>
+      <c r="F2" t="str">
+        <f>IF(OR(C2&gt;=130,D2&gt;=5),"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>110</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3" t="str">
+        <f t="shared" ref="E3:E10" si="0">IF(AND(C3&gt;=130,D3&gt;=5),"Yes","No")</f>
+        <v>No</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F10" si="1">IF(OR(C3&gt;=130,D3&gt;=5),"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>169</v>
+      </c>
+      <c r="D4">
+        <v>9</v>
+      </c>
+      <c r="E4" t="str">
+        <f t="shared" si="0"/>
+        <v>Yes</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>143</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>140</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6" t="str">
+        <f t="shared" si="0"/>
+        <v>Yes</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>179</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>136</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>164</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10">
+        <v>102</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Demo.xlsx
+++ b/Demo.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUVRAJ\Desktop\My Activities\GitHub\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08ACABF2-5ED0-4012-AB1A-1DA1C99819A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDC07DE-822A-4E74-AB60-510500094B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Nested_If" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="33">
   <si>
     <t>Sr. No</t>
   </si>
@@ -122,6 +123,21 @@
   </si>
   <si>
     <t>Or condition</t>
+  </si>
+  <si>
+    <t>%Avg</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Grades</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>Sub Passing</t>
   </si>
 </sst>
 </file>
@@ -157,10 +173,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -522,7 +537,7 @@
         <f>AVERAGE(C2:E2)</f>
         <v>71</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <f>F2/300%</f>
         <v>71</v>
       </c>
@@ -563,7 +578,7 @@
         <f t="shared" ref="I3:I6" si="3">AVERAGE(C3:E3)</f>
         <v>72</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <f t="shared" ref="J3:J6" si="4">F3/300%</f>
         <v>72</v>
       </c>
@@ -604,7 +619,7 @@
         <f t="shared" si="3"/>
         <v>83.666666666666671</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <f t="shared" si="4"/>
         <v>83.666666666666671</v>
       </c>
@@ -645,7 +660,7 @@
         <f t="shared" si="3"/>
         <v>63</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <f t="shared" si="4"/>
         <v>63</v>
       </c>
@@ -686,7 +701,7 @@
         <f t="shared" si="3"/>
         <v>72.333333333333329</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <f t="shared" si="4"/>
         <v>72.333333333333329</v>
       </c>
@@ -701,6 +716,408 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB29DE8-5959-4658-88AF-368C7BADC88A}">
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>90</v>
+      </c>
+      <c r="D2">
+        <v>79</v>
+      </c>
+      <c r="E2">
+        <v>44</v>
+      </c>
+      <c r="F2" t="str">
+        <f>IF(AND(C2&gt;=35,D2&gt;=35,E2&gt;=35),"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="G2">
+        <f>SUM(C2:E2)</f>
+        <v>213</v>
+      </c>
+      <c r="H2" s="1">
+        <f>G2/300*100</f>
+        <v>71</v>
+      </c>
+      <c r="I2" t="str">
+        <f>IF(F2="Fail","Fail",IF(H2&gt;=90,"O",IF(H2&gt;=80,"A",IF(H2&gt;=65,"B",IF(H2&gt;=50,"C",IF(H2&gt;=35,"D","Fail"))))))</f>
+        <v>B</v>
+      </c>
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>48</v>
+      </c>
+      <c r="D3">
+        <v>91</v>
+      </c>
+      <c r="E3">
+        <v>77</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F11" si="0">IF(AND(C3&gt;=35,D3&gt;=35,E3&gt;=35),"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G6" si="1">SUM(C3:E3)</f>
+        <v>216</v>
+      </c>
+      <c r="H3" s="1">
+        <f t="shared" ref="H3:H11" si="2">G3/300*100</f>
+        <v>72</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I11" si="3">IF(F3="Fail","Fail",IF(H3&gt;=90,"O",IF(H3&gt;=80,"A",IF(H3&gt;=65,"B",IF(H3&gt;=50,"C",IF(H3&gt;=35,"D","Fail"))))))</f>
+        <v>B</v>
+      </c>
+      <c r="L3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>94</v>
+      </c>
+      <c r="D4">
+        <v>77</v>
+      </c>
+      <c r="E4">
+        <v>80</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>251</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="2"/>
+        <v>83.666666666666671</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="3"/>
+        <v>A</v>
+      </c>
+      <c r="L4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>90</v>
+      </c>
+      <c r="D5">
+        <v>44</v>
+      </c>
+      <c r="E5">
+        <v>55</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>189</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="3"/>
+        <v>C</v>
+      </c>
+      <c r="L5" t="s">
+        <v>8</v>
+      </c>
+      <c r="M5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>62</v>
+      </c>
+      <c r="D6">
+        <v>78</v>
+      </c>
+      <c r="E6">
+        <v>77</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>217</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="2"/>
+        <v>72.333333333333343</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="3"/>
+        <v>B</v>
+      </c>
+      <c r="L6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>88</v>
+      </c>
+      <c r="D7">
+        <v>33</v>
+      </c>
+      <c r="E7">
+        <v>48</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+      <c r="G7">
+        <f t="shared" ref="G7:G11" si="4">SUM(C7:E7)</f>
+        <v>169</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="2"/>
+        <v>56.333333333333336</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>47</v>
+      </c>
+      <c r="D8">
+        <v>97</v>
+      </c>
+      <c r="E8">
+        <v>75</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="4"/>
+        <v>219</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="2"/>
+        <v>73</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="3"/>
+        <v>B</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>50</v>
+      </c>
+      <c r="D9">
+        <v>40</v>
+      </c>
+      <c r="E9">
+        <v>80</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>Pass</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="4"/>
+        <v>170</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="2"/>
+        <v>56.666666666666664</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="3"/>
+        <v>C</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>41</v>
+      </c>
+      <c r="E10">
+        <v>79</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="4"/>
+        <v>135</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11">
+        <v>61</v>
+      </c>
+      <c r="D11">
+        <v>64</v>
+      </c>
+      <c r="E11">
+        <v>14</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="4"/>
+        <v>139</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="2"/>
+        <v>46.333333333333329</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{269507E9-BEC7-4583-B3E5-5ECEC7CDD939}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -846,7 +1263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF93C26-F917-4F20-A5B4-CE61275C5F48}">
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Demo.xlsx
+++ b/Demo.xlsx
@@ -1,37 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUVRAJ\Desktop\My Activities\GitHub\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2562C37E-FD1F-4C00-A90E-BEF6668E4F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB17F211-F320-41A2-A18A-DF544732B935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Nested_If" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet6" sheetId="6" r:id="rId3"/>
+    <sheet name="pivot" sheetId="6" r:id="rId3"/>
     <sheet name="Conditional_Formatting" sheetId="5" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId5"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Conditional_Formatting!$A$1:$N$1288</definedName>
+    <definedName name="Slicer_City">#N/A</definedName>
     <definedName name="Slicer_Product_Category">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
         <x14:slicerCache r:id="rId8"/>
+        <x14:slicerCache r:id="rId9"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -1450,39 +1452,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1513,7 +1487,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Demo.xlsx]Sheet6!PivotTable1</c:name>
+    <c:name>[Demo.xlsx]pivot!PivotTable1</c:name>
     <c:fmtId val="21"/>
   </c:pivotSource>
   <c:chart>
@@ -1605,6 +1579,68 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -1617,7 +1653,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet6!$B$3</c:f>
+              <c:f>pivot!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1636,9 +1672,106 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-249A-407F-8823-0E39996D6D76}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-249A-407F-8823-0E39996D6D76}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-249A-407F-8823-0E39996D6D76}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-249A-407F-8823-0E39996D6D76}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-249A-407F-8823-0E39996D6D76}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet6!$A$4:$A$9</c:f>
+              <c:f>pivot!$A$4:$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -1661,24 +1794,24 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet6!$B$4:$B$9</c:f>
+              <c:f>pivot!$B$4:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>6624561.2000000002</c:v>
+                  <c:v>7883141.9499999993</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6067249.4000000013</c:v>
+                  <c:v>6139768.0499999989</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6220012.0499999998</c:v>
+                  <c:v>6022418.4999999991</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4731861.4499999993</c:v>
+                  <c:v>5743336.9500000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6537374.0000000019</c:v>
+                  <c:v>5856543.6000000015</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1921,6 +2054,10 @@
       <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Demo.xlsx]pivot!PivotTable1</c:name>
+    <c:fmtId val="27"/>
+  </c:pivotSource>
   <c:chart>
     <c:title>
       <c:overlay val="0"/>
@@ -1936,7 +2073,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1953,59 +2090,825 @@
       </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
-    <c:view3D>
-      <c:rotX val="30"/>
-      <c:rotY val="0"/>
-      <c:depthPercent val="100"/>
-      <c:rAngAx val="0"/>
-    </c:view3D>
-    <c:floor>
-      <c:thickness val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
-      </c:spPr>
-    </c:floor>
-    <c:sideWall>
-      <c:thickness val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
-      </c:spPr>
-    </c:sideWall>
-    <c:backWall>
-      <c:thickness val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
-      </c:spPr>
-    </c:backWall>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:xForSave val="1"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:xForSave val="1"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:xForSave val="1"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:xForSave val="1"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:xForSave val="1"/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
-      <c:pie3DChart>
+      <c:pieChart>
         <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>pivot!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-BCAB-4971-9A06-B0BF6FB3C04E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-BCAB-4971-9A06-B0BF6FB3C04E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-BCAB-4971-9A06-B0BF6FB3C04E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-BCAB-4971-9A06-B0BF6FB3C04E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-BCAB-4971-9A06-B0BF6FB3C04E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-BCAB-4971-9A06-B0BF6FB3C04E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-BCAB-4971-9A06-B0BF6FB3C04E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-BCAB-4971-9A06-B0BF6FB3C04E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-BCAB-4971-9A06-B0BF6FB3C04E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-BCAB-4971-9A06-B0BF6FB3C04E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>pivot!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Bangalore</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Delhi</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Hyderabad</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Mumbai</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Pune</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>pivot!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>7883141.9499999993</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6139768.0499999989</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6022418.4999999991</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5743336.9500000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5856543.6000000015</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BCAB-4971-9A06-B0BF6FB3C04E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
-      </c:pie3DChart>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -2014,37 +2917,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -2086,6 +2958,21 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
 </c:chartSpace>
 </file>
 
@@ -2673,7 +3560,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="262">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="259">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2684,7 +3571,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -2696,17 +3583,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
@@ -2730,29 +3606,25 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
+      <cs:styleClr val="auto"/>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <cs:styleClr val="auto"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -2760,50 +3632,65 @@
       </a:solidFill>
       <a:ln>
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" b="1" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="10000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+      <a:scene3d>
+        <a:camera prst="orthographicFront"/>
+        <a:lightRig rig="threePt" dir="t"/>
+      </a:scene3d>
+      <a:sp3d>
+        <a:bevelT w="127000" h="127000"/>
+        <a:bevelB w="127000" h="127000"/>
+      </a:sp3d>
     </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
@@ -2813,7 +3700,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="28575" cap="rnd">
@@ -2825,25 +3712,26 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
@@ -2851,7 +3739,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -3056,7 +3944,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
@@ -3064,7 +3952,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -3108,7 +3996,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -3124,7 +4012,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -3206,8 +4094,8 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="Product_Category">
@@ -3230,7 +4118,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3307,25 +4195,103 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="City">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B036E06-AD54-79A2-214F-7DAB415F4943}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="City"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2278380" y="2979420"/>
+              <a:ext cx="1828800" cy="2466975"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>179070</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>179070</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{553CAAF5-40D4-B489-7F02-D10EBF6D2A64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A32B890-B6F7-A5F8-AA66-1C8317E07EBA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3409,6 +4375,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition pivotCacheId="1361752105"/>
     </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
@@ -24011,7 +24980,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{59D4917F-3B08-4EEF-9FE8-575DF973C0CD}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{59D4917F-3B08-4EEF-9FE8-575DF973C0CD}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="36">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -24030,8 +24999,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item x="2"/>
-        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item x="0"/>
         <item h="1" x="1"/>
         <item t="default"/>
       </items>
@@ -24074,7 +25043,7 @@
   <dataFields count="1">
     <dataField name="Sum of Total_Sales" fld="10" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="2">
+  <chartFormats count="13">
     <chartFormat chart="15" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -24089,6 +25058,135 @@
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
@@ -24114,9 +25212,28 @@
   <data>
     <tabular pivotCacheId="1361752105">
       <items count="3">
+        <i x="2"/>
+        <i x="0" s="1"/>
+        <i x="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_City" xr10:uid="{6B1258F7-5D96-470E-A832-3F6E2DC75B11}" sourceName="City">
+  <pivotTables>
+    <pivotTable tabId="6" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1361752105">
+      <items count="5">
+        <i x="4" s="1"/>
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+        <i x="3" s="1"/>
         <i x="2" s="1"/>
-        <i x="0"/>
-        <i x="1"/>
       </items>
     </tabular>
   </data>
@@ -24126,6 +25243,7 @@
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
   <slicer name="Product_Category" xr10:uid="{D12CB65B-4FE7-4947-82E5-BCA432A9F8AE}" cache="Slicer_Product_Category" caption="Product_Category" rowHeight="234950"/>
+  <slicer name="City" xr10:uid="{7EA9044C-86BA-4416-A5F5-CB6BBF8FE669}" cache="Slicer_City" caption="City" rowHeight="234950"/>
 </slicers>
 </file>
 
@@ -25075,7 +26193,7 @@
         <v>83</v>
       </c>
       <c r="B4" s="4">
-        <v>6624561.2000000002</v>
+        <v>7883141.9499999993</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -25083,7 +26201,7 @@
         <v>56</v>
       </c>
       <c r="B5" s="4">
-        <v>6067249.4000000013</v>
+        <v>6139768.0499999989</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -25091,7 +26209,7 @@
         <v>49</v>
       </c>
       <c r="B6" s="4">
-        <v>6220012.0499999998</v>
+        <v>6022418.4999999991</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -25099,7 +26217,7 @@
         <v>70</v>
       </c>
       <c r="B7" s="4">
-        <v>4731861.4499999993</v>
+        <v>5743336.9500000002</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -25107,7 +26225,7 @@
         <v>61</v>
       </c>
       <c r="B8" s="4">
-        <v>6537374.0000000019</v>
+        <v>5856543.6000000015</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -25115,7 +26233,7 @@
         <v>447</v>
       </c>
       <c r="B9" s="4">
-        <v>30181058.100000001</v>
+        <v>31645209.049999997</v>
       </c>
     </row>
   </sheetData>
@@ -81825,7 +82943,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1288" xr:uid="{702AE400-6E0E-4595-9FE5-69554DF9F497}"/>
   <conditionalFormatting sqref="A2:N1288">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$D2="Delhi"</formula>
